--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_CR_BRD-11_Change_Request_Register_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_CR_BRD-11_Change_Request_Register_v1.0.xlsx
@@ -6357,7 +6357,7 @@
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Proposed wording for BDOI's approval: NT-17 "New rule &lt;rule&gt;: &lt;reason&gt;" instead of "The new rule of rule &lt;rule&gt;"; NT-13 "(emergency role edit)" instead of the setting code shown today; NT-18 "&lt;user&gt; asks to change it from ... to ..." as written in Annex L of version 1.2.</t>
+          <t>Proposed wording for BDOI's approval: NT-17 "New rule &lt;rule&gt;: &lt;reason&gt;" instead of "The new rule of rule &lt;rule&gt;"; NT-13 "(emergency role edit)" instead of the setting code shown today; NT-18: the system says "&lt;user&gt; requests a change from ... to ..." while Annex L of version 1.2 showed "asks to change it from"; Annex L now quotes the system and BDOI chooses the wording.</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_CR_BRD-11_Change_Request_Register_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_CR_BRD-11_Change_Request_Register_v1.0.xlsx
@@ -851,7 +851,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>9 October 2026</t>
+          <t>10 October 2026</t>
         </is>
       </c>
     </row>
@@ -3837,7 +3837,7 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Option (a): UIDM-ISC provisions the user accounts (create, deactivate, reactivate) through the standard provisioning interface, each change logged with its UIDM request number; the assignment and change of group profiles and the group-profile requests stay as requests in the system under four eyes. FRUM.009 to FRUM.011 then apply to the changes not requested in UIDM; all of them apply if BDOI keeps every request in the system. (BIBS reference FRS: FR-UA-010 to FR-UA-020 and FR-UA-030 to FR-UA-034: every access change is a request in the system, decided by a chosen approver under four eyes; the UIDM-ISC option is open (CLR-UA-03).)</t>
+          <t>Option (a): UIDM-ISC provisions the user accounts (create, deactivate, reactivate) through the standard provisioning interface, each change logged with its UIDM request number; the assignment and change of group profiles and the group-profile requests stay as requests in the system under four eyes. FRUM.009 to FRUM.011 then apply to the changes not requested in UIDM; all of them apply if BDOI keeps every request in the system. (BIBS reference FRS: FR-UA-010 to FR-UA-020 and FR-UA-030 to FR-UA-034: every access change is a request in the system, decided by a chosen approver under four eyes; the UIDM-ISC option is open (CLR-UA-03).) Available in BIBS: user accounts are created, updated, deactivated and reactivated from the Enterprise SSO and UIDM-ISC events (setting on by default, BDOI's text) or only through approved requests; the group profiles named in a UIDM-ISC event are applied only when a second setting is on (default off, option a).</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Create the user from the UIDM-ISC provisioning (which carries the SSO account) or from an approved enrolment; the Windows ID is checked against EIAM at the first sign-in. A look-up of the SSO directory on the enrolment screen is a change to the system for BDOI to decide. (BIBS reference FRS: FR-UA-003, FR-UA-011: the system never creates a user from a sign-in; the EIAM identity is linked to an existing active user by the Windows ID or the UPN (CLR-UA-22); the user is created by an approved enrolment or, as proposed, by UIDM-ISC provisioning.)</t>
+          <t>Create the user from the UIDM-ISC provisioning (which carries the SSO account) or from an approved enrolment; the Windows ID is checked against EIAM at the first sign-in. A look-up of the SSO directory on the enrolment screen is a change to the system for BDOI to decide. (BIBS reference FRS: FR-UA-003, FR-UA-011: the system never creates a user from a sign-in; the EIAM identity is linked to an existing active user by the Windows ID or the UPN (CLR-UA-22); the user is created by an approved enrolment or, as proposed, by UIDM-ISC provisioning.) Available in BIBS: the user is created from an active Enterprise SSO account when the provisioning setting is on (default).</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Keep both - BDOI's message and Log In button after the inactivity sign-out (adopt the wording), and the warning before the fixed end of the session that the BRD asks. (BIBS reference FRS: FR-UA-002: sign-out after 30 minutes of inactivity with the warning at 15 minutes; a separate warning 30 minutes before the fixed end of the session.)</t>
+          <t>Keep both - BDOI's message and Log In button after the inactivity sign-out (adopt the wording), and the warning before the fixed end of the session that the BRD asks. (BIBS reference FRS: FR-UA-002: sign-out after 30 minutes of inactivity with the warning at 15 minutes; a separate warning 30 minutes before the fixed end of the session.) Available in BIBS: after the inactivity sign-out the page 'Your session timed out' with Log In is shown (setting on by default, BDOI's text) or a message on the Login page.</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Adopt BDOI's text and buttons (a screen text change, no rule change). (BIBS reference FRS: FR-UA-002 and the session dialog of the screens: "For your security the system signs you out in n minute(s)..." with the system's own buttons.)</t>
+          <t>Adopt BDOI's text and buttons (a screen text change, no rule change). (BIBS reference FRS: FR-UA-002 and the session dialog of the screens: "For your security the system signs you out in n minute(s)..." with the system's own buttons.) Available in BIBS: the inactivity warning uses BDOI's wording and the buttons Stay Logged In and Log Out (setting on by default) or the earlier wording.</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Adopt 10 for the local accounts (a setting value, no change). (BIBS reference FRS: FR-UA-005: history of 8 for local accounts (value to confirm, UQ08).)</t>
+          <t>Adopt 10 for the local accounts (a setting value, no change). (BIBS reference FRS: FR-UA-005: history of 8 for local accounts (value to confirm, UQ08).) Available in BIBS: the number of previous passwords that may not be reused is a security setting, delivered at 10 (BDOI's text).</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>SSO users: BDOI's rule (no reset in the application). Break-glass accounts: reset by a second administrator only; the self-service link switched off in production. (BIBS reference FRS: FR-UA-005: for local accounts, an administrator reset and a self-service reset link; none for SSO users.)</t>
+          <t>SSO users: BDOI's rule (no reset in the application). Break-glass accounts: reset by a second administrator only; the self-service link switched off in production. (BIBS reference FRS: FR-UA-005: for local accounts, an administrator reset and a self-service reset link; none for SSO users.) Available in BIBS: no forgotten-password link and reset by another System Administrator only (setting on by default, BDOI's text) or the self-service reset of local accounts.</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>With option (a), a leaver from UIDM-ISC deactivates the user and ends the open sessions at once (change to the system); a deactivation request does the same on approval. (BIBS reference FRS: FR-UA-013, FR-UA-006: deactivation by a request or the dormant-user job; EIAM refuses a disabled BDO account at the next sign-in; the open session ends at the inactivity sign-out or the session expiry.)</t>
+          <t>With option (a), a leaver from UIDM-ISC deactivates the user and ends the open sessions at once (change to the system); a deactivation request does the same on approval. (BIBS reference FRS: FR-UA-013, FR-UA-006: deactivation by a request or the dormant-user job; EIAM refuses a disabled BDO account at the next sign-in; the open session ends at the inactivity sign-out or the session expiry.) Available in BIBS: access is revoked and restored from the Enterprise SSO status when the provisioning setting is on (default).</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Show on each user the last provisioning event (time, source, UIDM request number); refuse a failed provisioning call back to UIDM-ISC and alert the System Administrator; replace the on-demand synchronisation by a re-send from UIDM-ISC. (BIBS reference FRS: None; the UIDM-ISC option (a) pushes changes to the system; the Users screen shows the last sign-in.)</t>
+          <t>Show on each user the last provisioning event (time, source, UIDM request number); refuse a failed provisioning call back to UIDM-ISC and alert the System Administrator; replace the on-demand synchronisation by a re-send from UIDM-ISC. (BIBS reference FRS: None; the UIDM-ISC option (a) pushes changes to the system; the Users screen shows the last sign-in.) Available in BIBS: synchronisation from the Enterprise SSO runs on each event and on demand when the provisioning setting is on (default).</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Keep the rules at group-profile level (what one user may hold); BDOI lists the permission pairs it means and they become rules between profiles. (BIBS reference FRS: FR-UA-053: separation-of-duties rules name pairs of group profiles one user may not hold, maintained by the Business Administrator and authorised by Information Security; FR-UA-041 refuses a permission both added and removed.)</t>
+          <t>Keep the rules at group-profile level (what one user may hold); BDOI lists the permission pairs it means and they become rules between profiles. (BIBS reference FRS: FR-UA-053: separation-of-duties rules name pairs of group profiles one user may not hold, maintained by the Business Administrator and authorised by Information Security; FR-UA-041 refuses a permission both added and removed.) Available in BIBS: the conflicting permission combinations are rules maintained by Information Security under a second approval.</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>Adopt BDOI's file names (a change of the download name). (BIBS reference FRS: FR-UA-060 to FR-UA-063: report name, generated by, coverage and time generated in the header; the file name is not specified.)</t>
+          <t>Adopt BDOI's file names (a change of the download name). (BIBS reference FRS: FR-UA-060 to FR-UA-063: report name, generated by, coverage and time generated in the header; the file name is not specified.) Available in BIBS: the exports are named by BDOI's convention &lt;name&gt;_MMDDYYYY (setting on by default) or by the report code.</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Add as FRUM.013.01. (BIBS reference FRS: FR-UA-070: notices to the approver, the requester and the affected user, in the system and by e-mail.)</t>
+          <t>Add as FRUM.013.01. (BIBS reference FRS: FR-UA-070: notices to the approver, the requester and the affected user, in the system and by e-mail.) Available in BIBS: the notices of access requests are also e-mailed by each user's notification preference (setting on by default) or shown in the system only.</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_CR_BRD-11_Change_Request_Register_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_CR_BRD-11_Change_Request_Register_v1.0.xlsx
@@ -6033,7 +6033,7 @@
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>The screenshot of New Request in Annex J (J.7) was taken on 29-Sep-2026 and still shows the earlier check-box list of group profiles. The screen now offers the profile picker described in FRUM.009.02 and J.7 (profiles by business area, search, details, chosen profiles listed apart, Privileged marker, separation-of-duties warning). The screenshot is replaced at the next issue.</t>
+          <t>The screen offers the profile picker described in FRUM.009.02 and J.7 (profiles by business area, search, details, chosen profiles listed apart, Privileged marker, separation-of-duties warning). Resolved in version 1.3: every screenshot of Annex J was taken again on 10-Oct-2026 and shows the picker.</t>
         </is>
       </c>
       <c r="E66" s="12" t="inlineStr">

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_CR_BRD-11_Change_Request_Register_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_CR_BRD-11_Change_Request_Register_v1.0.xlsx
@@ -3837,7 +3837,7 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Option (a): UIDM-ISC provisions the user accounts (create, deactivate, reactivate) through the standard provisioning interface, each change logged with its UIDM request number; the assignment and change of group profiles and the group-profile requests stay as requests in the system under four eyes. FRUM.009 to FRUM.011 then apply to the changes not requested in UIDM; all of them apply if BDOI keeps every request in the system. (BIBS reference FRS: FR-UA-010 to FR-UA-020 and FR-UA-030 to FR-UA-034: every access change is a request in the system, decided by a chosen approver under four eyes; the UIDM-ISC option is open (CLR-UA-03).) Available in BIBS: user accounts are created, updated, deactivated and reactivated from the Enterprise SSO and UIDM-ISC events (setting on by default, BDOI's text) or only through approved requests; the group profiles named in a UIDM-ISC event are applied only when a second setting is on (default off, option a).</t>
+          <t>Option (a): UIDM-ISC provisions the user accounts (create, deactivate, reactivate) through the standard provisioning interface, each change logged with its UIDM request number; the assignment and change of group profiles and the group-profile requests stay as requests in the system under four eyes. FRUM.009 to FRUM.011 then apply to the changes not requested in UIDM; all of them apply if BDOI keeps every request in the system. Proposed behaviour: FRUM.009.01 to FRUM.009.10 and FRUM.010.01 to FRUM.010.05: every access change is a request in the system, decided by a chosen approver under four eyes; the UIDM-ISC option is open (CLR-UA-03). Available in BIBS: user accounts are created, updated, deactivated and reactivated from the Enterprise SSO and UIDM-ISC events (setting on by default, BDOI's text) or only through approved requests; the group profiles named in a UIDM-ISC event are applied only when a second setting is on (default off, option a).</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Assign roles through the request with four eyes; read BDOI's "authorized users" as the requester and the approver together. (BIBS reference FRS: FR-UA-011, FR-UA-012, FR-UA-031: group profiles are assigned through an enrolment or modify request approved by another user; a direct change is an audited emergency of the System Administrator (FR-UA-045, FR-UA-052).)</t>
+          <t>Assign roles through the request with four eyes; read BDOI's "authorized users" as the requester and the approver together. Proposed behaviour: FRUM.002.01, FRUM.009.02, FRUM.003.01, FRUM.009.03, FRUM.002.01, FRUM.010.02: group profiles are assigned through an enrolment or modify request approved by another user; a direct change is an audited emergency of the System Administrator (FRUM.005.01, FRUM.005.04, FRUM.002.01, FRUM.002.03).</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Keep BDOI's capabilities as the System Administrator's implementation of an approved group-profile request (FRUM.005.02 to.04, FRUM.006.04). (BIBS reference FRS: FR-UA-040 to FR-UA-045: the Business Administrator requests, the approvers decide in order, the System Administrator implements; a direct role edit is refused unless the emergency setting is on.)</t>
+          <t>Keep BDOI's capabilities as the System Administrator's implementation of an approved group-profile request (FRUM.005.02 to.04, FRUM.006.04). Proposed behaviour: FRUM.005.01, FRUM.005.02 to FRUM.005.01, FRUM.005.04: the Business Administrator requests, the approvers decide in order, the System Administrator implements; a direct role edit is refused unless the emergency setting is on.</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Create the user from the UIDM-ISC provisioning (which carries the SSO account) or from an approved enrolment; the Windows ID is checked against EIAM at the first sign-in. A look-up of the SSO directory on the enrolment screen is a change to the system for BDOI to decide. (BIBS reference FRS: FR-UA-003, FR-UA-011: the system never creates a user from a sign-in; the EIAM identity is linked to an existing active user by the Windows ID or the UPN (CLR-UA-22); the user is created by an approved enrolment or, as proposed, by UIDM-ISC provisioning.) Available in BIBS: the user is created from an active Enterprise SSO account when the provisioning setting is on (default).</t>
+          <t>Create the user from the UIDM-ISC provisioning (which carries the SSO account) or from an approved enrolment; the Windows ID is checked against EIAM at the first sign-in. A look-up of the SSO directory on the enrolment screen is a change to the system for BDOI to decide. Proposed behaviour: FRUM.001.02, FRUM.001.06, FRUM.002.01, FRUM.009.02: the system never creates a user from a sign-in; the EIAM identity is linked to an existing active user by the Windows ID or the UPN (CLR-UA-22); the user is created by an approved enrolment or, as proposed, by UIDM-ISC provisioning. Available in BIBS: the user is created from an active Enterprise SSO account when the provisioning setting is on (default).</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Keep the Windows ID unique on its own, which is stricter than the combination and also refuses BDOI's duplicates; warn when the e-mail address is already used by another user. (BIBS reference FRS: FR-UA-011: the user ID is unique and the Windows ID is unique on its own ("Windows ID &lt;id&gt; belongs to another user").)</t>
+          <t>Keep the Windows ID unique on its own, which is stricter than the combination and also refuses BDOI's duplicates; warn when the e-mail address is already used by another user. Proposed behaviour: FRUM.002.01, FRUM.009.02: the user ID is unique and the Windows ID is unique on its own ("Windows ID &lt;id&gt; belongs to another user").</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Keep both values; the reports and the audit log show the user ID and the Windows ID. (BIBS reference FRS: FR-UA-011, FR-UA-052: a user ID in the BDOI format (a letter and nine digits) and the Windows ID held separately for the single sign-on match.)</t>
+          <t>Keep both values; the reports and the audit log show the user ID and the Windows ID. Proposed behaviour: FRUM.002.01, FRUM.009.02, FRUM.002.01, FRUM.002.03: a user ID in the BDOI format (a letter and nine digits) and the Windows ID held separately for the single sign-on match.</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Keep both - BDOI's message and Log In button after the inactivity sign-out (adopt the wording), and the warning before the fixed end of the session that the BRD asks. (BIBS reference FRS: FR-UA-002: sign-out after 30 minutes of inactivity with the warning at 15 minutes; a separate warning 30 minutes before the fixed end of the session.) Available in BIBS: after the inactivity sign-out the page 'Your session timed out' with Log In is shown (setting on by default, BDOI's text) or a message on the Login page.</t>
+          <t>Keep both - BDOI's message and Log In button after the inactivity sign-out (adopt the wording), and the warning before the fixed end of the session that the BRD asks. Proposed behaviour: FRUM.001.01, FRUM.001.03: sign-out after 30 minutes of inactivity with the warning at 15 minutes; a separate warning 30 minutes before the fixed end of the session. Available in BIBS: after the inactivity sign-out the page 'Your session timed out' with Log In is shown (setting on by default, BDOI's text) or a message on the Login page.</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Adopt BDOI's text and buttons (a screen text change, no rule change). (BIBS reference FRS: FR-UA-002 and the session dialog of the screens: "For your security the system signs you out in n minute(s)..." with the system's own buttons.) Available in BIBS: the inactivity warning uses BDOI's wording and the buttons Stay Logged In and Log Out (setting on by default) or the earlier wording.</t>
+          <t>Adopt BDOI's text and buttons (a screen text change, no rule change). Proposed behaviour: FRUM.001.01, FRUM.001.03 and the session dialog of the screens: "For your security the system signs you out in n minute(s)..." with the system's own buttons. Available in BIBS: the inactivity warning uses BDOI's wording and the buttons Stay Logged In and Log Out (setting on by default) or the earlier wording.</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>EIAM's lock-out set to 3 invalid tries for BDO accounts (BDOI IT to confirm); 3 in the application for the break-glass accounts. (BIBS reference FRS: FR-UA-001, CLR-UA-25: with single sign-on the EIAM lock-out policy applies; the application locks the local (break-glass) accounts after 3 failed attempts.)</t>
+          <t>EIAM's lock-out set to 3 invalid tries for BDO accounts (BDOI IT to confirm); 3 in the application for the break-glass accounts. Proposed behaviour: FRUM.001.01, FRUM.001.02, CLR-UA-25: with single sign-on the EIAM lock-out policy applies; the application locks the local (break-glass) accounts after 3 failed attempts.</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Adopt 10 for the local accounts (a setting value, no change). (BIBS reference FRS: FR-UA-005: history of 8 for local accounts (value to confirm, UQ08).) Available in BIBS: the number of previous passwords that may not be reused is a security setting, delivered at 10 (BDOI's text).</t>
+          <t>Adopt 10 for the local accounts (a setting value, no change). Proposed behaviour: FRUM-004.01, FRUM-004.02: history of 8 for local accounts (value to confirm, UQ08). Available in BIBS: the number of previous passwords that may not be reused is a security setting, delivered at 10 (BDOI's text).</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>SSO users: BDOI's rule (no reset in the application). Break-glass accounts: reset by a second administrator only; the self-service link switched off in production. (BIBS reference FRS: FR-UA-005: for local accounts, an administrator reset and a self-service reset link; none for SSO users.) Available in BIBS: no forgotten-password link and reset by another System Administrator only (setting on by default, BDOI's text) or the self-service reset of local accounts.</t>
+          <t>SSO users: BDOI's rule (no reset in the application). Break-glass accounts: reset by a second administrator only; the self-service link switched off in production. Proposed behaviour: FRUM-004.01, FRUM-004.02: for local accounts, an administrator reset and a self-service reset link; none for SSO users. Available in BIBS: no forgotten-password link and reset by another System Administrator only (setting on by default, BDOI's text) or the self-service reset of local accounts.</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>Keep the single message of the local sign-in; keep the not-linked message of single sign-on (the identity is already proven by EIAM, and the user needs to know to call the administrator), for Information Security to confirm. (BIBS reference FRS: FR-UA-001: one message for a wrong password, a locked and a deactivated account ("Invalid user name or password"); FR-UA-003: "Your sign-in was accepted by your organisation, but it is not linked to an active user of this system. Contact your administrator.")</t>
+          <t>Keep the single message of the local sign-in; keep the not-linked message of single sign-on (the identity is already proven by EIAM, and the user needs to know to call the administrator), for Information Security to confirm. Proposed behaviour: FRUM.001.01, FRUM.001.02: one message for a wrong password, a locked and a deactivated account ("Invalid user name or password"); FRUM.001.02, FRUM.001.06: "Your sign-in was accepted by your organisation, but it is not linked to an active user of this system. Contact your administrator."</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>With option (a), a leaver from UIDM-ISC deactivates the user and ends the open sessions at once (change to the system); a deactivation request does the same on approval. (BIBS reference FRS: FR-UA-013, FR-UA-006: deactivation by a request or the dormant-user job; EIAM refuses a disabled BDO account at the next sign-in; the open session ends at the inactivity sign-out or the session expiry.) Available in BIBS: access is revoked and restored from the Enterprise SSO status when the provisioning setting is on (default).</t>
+          <t>With option (a), a leaver from UIDM-ISC deactivates the user and ends the open sessions at once (change to the system); a deactivation request does the same on approval. Proposed behaviour: FRUM.003.02.01, FRUM.009.04, FRUM.003.02.01, FRUM.003.04: deactivation by a request or the dormant-user job; EIAM refuses a disabled BDO account at the next sign-in; the open session ends at the inactivity sign-out or the session expiry. Available in BIBS: access is revoked and restored from the Enterprise SSO status when the provisioning setting is on (default).</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Show on each user the last provisioning event (time, source, UIDM request number); refuse a failed provisioning call back to UIDM-ISC and alert the System Administrator; replace the on-demand synchronisation by a re-send from UIDM-ISC. (BIBS reference FRS: None; the UIDM-ISC option (a) pushes changes to the system; the Users screen shows the last sign-in.) Available in BIBS: synchronisation from the Enterprise SSO runs on each event and on demand when the provisioning setting is on (default).</t>
+          <t>Show on each user the last provisioning event (time, source, UIDM request number); refuse a failed provisioning call back to UIDM-ISC and alert the System Administrator; replace the on-demand synchronisation by a re-send from UIDM-ISC. Proposed behaviour: None; the UIDM-ISC option (a) pushes changes to the system; the Users screen shows the last sign-in. Available in BIBS: synchronisation from the Enterprise SSO runs on each event and on demand when the provisioning setting is on (default).</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Hold the data scope on the user record (unit, team, supervisor) as part of FRUM.002.03, with the values per persona from the User Access Matrix. (BIBS reference FRS: Roles and permissions only in the BRD-11 FRS; the record scope of each user (own, team, unit) is set in the data scope of the user and specified by each module FRS.)</t>
+          <t>Hold the data scope on the user record (unit, team, supervisor) as part of FRUM.002.03, with the values per persona from the User Access Matrix. Proposed behaviour: Roles and permissions only in the BRD-11 FRS; the record scope of each user (own, team, unit) is set in the data scope of the user and specified by each module FRS.</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Keep the rules at group-profile level (what one user may hold); BDOI lists the permission pairs it means and they become rules between profiles. (BIBS reference FRS: FR-UA-053: separation-of-duties rules name pairs of group profiles one user may not hold, maintained by the Business Administrator and authorised by Information Security; FR-UA-041 refuses a permission both added and removed.) Available in BIBS: the conflicting permission combinations are rules maintained by Information Security under a second approval.</t>
+          <t>Keep the rules at group-profile level (what one user may hold); BDOI lists the permission pairs it means and they become rules between profiles. Proposed behaviour: FRUM.006.03, FRUM.012.01: separation-of-duties rules name pairs of group profiles one user may not hold, maintained by the Business Administrator and authorised by Information Security; FRUM.006.01, FRUM.006.03 refuses a permission both added and removed. Available in BIBS: the conflicting permission combinations are rules maintained by Information Security under a second approval.</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Add as FRUM.010.05; BDOI names the high-privilege profiles and the working hours. (BIBS reference FRS: FR-UA-034: a change to a High or Admin profile, or one submitted or approved outside working hours, needs a second approver and raises an alert.)</t>
+          <t>Add as FRUM.010.05; BDOI names the high-privilege profiles and the working hours. Proposed behaviour: FRUM.010.05: a change to a High or Admin profile, or one submitted or approved outside working hours, needs a second approver and raises an alert.</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>Adopt BDOI's file names (a change of the download name). (BIBS reference FRS: FR-UA-060 to FR-UA-063: report name, generated by, coverage and time generated in the header; the file name is not specified.) Available in BIBS: the exports are named by BDOI's convention &lt;name&gt;_MMDDYYYY (setting on by default) or by the report code.</t>
+          <t>Adopt BDOI's file names (a change of the download name). Proposed behaviour: FRUM.007.01, FRUM.007.02 to FRUM.008.01, FRUM.008.01 (2nd): report name, generated by, coverage and time generated in the header; the file name is not specified. Available in BIBS: the exports are named by BDOI's convention &lt;name&gt;_MMDDYYYY (setting on by default) or by the report code.</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Add the role at the time and the source (IP) address to the audit entries (change to the system) and keep approved by and the request number; Annex H extended. (BIBS reference FRS: FR-UA-063, FR-UA-064: date, activity, from, to, done by, approved by, request number; the session log keeps the sign-in method and second factor.)</t>
+          <t>Add the role at the time and the source (IP) address to the audit entries (change to the system) and keep approved by and the request number; Annex H extended. Proposed behaviour: FRUM.008.01, FRUM.008.01 (2nd), FRUM.008.01, FRUM.008.04: date, activity, from, to, done by, approved by, request number; the session log keeps the sign-in method and second factor.</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Show the inactivity sign-out as action Inactivity and the session expiry as action Timeout in the User Access Audit Log. (BIBS reference FRS: FR-UA-004: the session log records the end reason (log-out, inactivity, session expiry, ended by an administrator, account locked); the audit log report can include log-ins and log-outs.)</t>
+          <t>Show the inactivity sign-out as action Inactivity and the session expiry as action Timeout in the User Access Audit Log. Proposed behaviour: FRUM.001.04, FRUM.001.05: the session log records the end reason (log-out, inactivity, session expiry, ended by an administrator, account locked); the audit log report can include log-ins and log-outs.</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
@@ -4557,7 +4557,7 @@
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Allow it, as both say, with the members listed on the request and notified. (BIBS reference FRS: FR-UA-042: the members lose its screens on implementation and are listed and notified; whether members must be moved first is open (UQ16, CLR-UA-07).)</t>
+          <t>Allow it, as both say, with the members listed on the request and notified. Proposed behaviour: FRUM.006.02.01, FRUM.006.04: the members lose its screens on implementation and are listed and notified; whether members must be moved first is open (UQ16, CLR-UA-07).</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Add as FRUM.005.03; BDOI names the approvers (UQ02). (BIBS reference FRS: FR-UA-044: one or more approvers in order; all must approve; any can reject or return.)</t>
+          <t>Add as FRUM.005.03; BDOI names the approvers (UQ02). Proposed behaviour: FRUM.005.01, FRUM.005.03: one or more approvers in order; all must approve; any can reject or return.</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Add as FRUM.009.10. (BIBS reference FRS: FR-UA-020: a request may carry an effective date; approved before it, it waits as Scheduled and is applied on the date.)</t>
+          <t>Add as FRUM.009.10. Proposed behaviour: FRUM.009.10: a request may carry an effective date; approved before it, it waits as Scheduled and is applied on the date.</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Add as FRUM.011; with option (a) the bulk request serves the group-profile changes and the go-live load of users. (BIBS reference FRS: FR-UA-019: a bulk request from a template, checked row by row, decided by one approver and applied line by line.)</t>
+          <t>Add as FRUM.011; with option (a) the bulk request serves the group-profile changes and the go-live load of users. Proposed behaviour: FRUM.011.01: a bulk request from a template, checked row by row, decided by one approver and applied line by line.</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Add as FRUM.013.01. (BIBS reference FRS: FR-UA-070: notices to the approver, the requester and the affected user, in the system and by e-mail.) Available in BIBS: the notices of access requests are also e-mailed by each user's notification preference (setting on by default) or shown in the system only.</t>
+          <t>Add as FRUM.013.01. Proposed behaviour: FRUM.013.01: notices to the approver, the requester and the affected user, in the system and by e-mail. Available in BIBS: the notices of access requests are also e-mailed by each user's notification preference (setting on by default) or shown in the system only.</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Add as FRUM.003.04 with the values of Information Security. (BIBS reference FRS: FR-UA-006: users without a sign-in for 90 days are deactivated by a daily job, with a notice 7 days before; System Administrators exempt.)</t>
+          <t>Add as FRUM.003.04 with the values of Information Security. Proposed behaviour: FRUM.003.02.01, FRUM.003.04: users without a sign-in for 90 days are deactivated by a daily job, with a notice 7 days before; System Administrators exempt.</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Hold the AD group for information and for the sign-in gate only; roles stay in the system. (BIBS reference FRS: CLR-UA-26: no Entra ID group is mapped to a role; roles change only through requests; a 'the system users' group may gate who reaches the system.)</t>
+          <t>Hold the AD group for information and for the sign-in gate only; roles stay in the system. Proposed behaviour: CLR-UA-26: no Entra ID group is mapped to a role; roles change only through requests; a 'the system users' group may gate who reaches the system.</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Take the union - add BDOI's hierarchy names, unit / segment, department, location and UIDM request number (change to the system for the fields not held) and keep the BRD's business unit group and user level. (BIBS reference FRS: FR-UA-011, FR-UA-052: user ID, Windows ID, full name, e-mail, home branch, business unit group, user level, group profiles, authorisation limit, status, last sign-in.)</t>
+          <t>Take the union - add BDOI's hierarchy names, unit / segment, department, location and UIDM request number (change to the system for the fields not held) and keep the BRD's business unit group and user level. Proposed behaviour: FRUM.002.01, FRUM.009.02, FRUM.002.01, FRUM.002.03: user ID, Windows ID, full name, e-mail, home branch, business unit group, user level, group profiles, authorisation limit, status, last sign-in.</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Annex P lists the rows that carry a function with the analyst's IDs UAM-NFR-nn of the BIBS FRS; the infrastructure rows are answered in the Technical Specification reviewed by BDOI IT.</t>
+          <t>Annex P lists the rows that carry a function with the IDs UAM-NFR-nn of Annex X; the infrastructure rows are answered in the Technical Specification reviewed by BDOI IT.</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>The numbered acceptance criteria added under each item are the basis of the BIBS test plan BRD-11 (Annex P); BDOI accepts or amends them with the review.</t>
+          <t>The numbered acceptance criteria added under each item are the basis of the test cases of the Test Cases and Traceability workbook (Annex P); BDOI accepts or amends them with the review.</t>
         </is>
       </c>
       <c r="E72" s="12" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>Our earlier questions that BDOI's FRS answers are no longer asked; each is listed with the BDOI clause that answers it in the Test Cases and Traceability workbook (sheet Answered in the BDOI FRS). Where BDOI's answer differs from the BRD, the decision stays in Annex Q.</t>
+          <t>The earlier questions that BDOI's FRS answers are no longer asked; each is listed with the BDOI clause that answers it in the Test Cases and Traceability workbook (sheet Answered in the BDOI FRS). Where BDOI's answer differs from the BRD, the decision stays in Annex Q.</t>
         </is>
       </c>
       <c r="E80" s="12" t="inlineStr">

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_CR_BRD-11_Change_Request_Register_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_CR_BRD-11_Change_Request_Register_v1.0.xlsx
@@ -851,7 +851,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>10 October 2026</t>
+          <t>11 October 2026</t>
         </is>
       </c>
     </row>
